--- a/exports/DIXON_full_report.xlsx
+++ b/exports/DIXON_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.68</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>5235.05</v>
+        <v>5133.5</v>
       </c>
       <c r="I2" t="n">
         <v>5178.087180905653</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.87</v>
+        <v>-3.78</v>
       </c>
       <c r="L2" t="n">
-        <v>2.88</v>
+        <v>4.03</v>
       </c>
       <c r="M2" t="n">
-        <v>0.53</v>
+        <v>1.24</v>
       </c>
       <c r="N2" t="n">
-        <v>2.39</v>
+        <v>4.49</v>
       </c>
       <c r="O2" t="n">
         <v>0.16</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.42</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44617.38541666666</v>
+        <v>44617.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>4244.7</v>
+        <v>4389</v>
       </c>
       <c r="I3" t="n">
         <v>4373.123034485779</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>17.31</v>
+        <v>14.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.82</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.41</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44669.38541666666</v>
+        <v>44669.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>4354.55</v>
+        <v>4318</v>
       </c>
       <c r="I4" t="n">
         <v>4330.430677517717</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.83333333333334</v>
+        <v>52</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.78</v>
+        <v>-1.62</v>
       </c>
       <c r="L4" t="n">
         <v>10.16</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.36</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44711.38541666666</v>
+        <v>44711.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>3565</v>
+        <v>3755</v>
       </c>
       <c r="I5" t="n">
         <v>3645.285990001653</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>41.83333333333334</v>
+        <v>42</v>
       </c>
       <c r="K5" t="n">
-        <v>17.44</v>
+        <v>13.04</v>
       </c>
       <c r="L5" t="n">
         <v>2.46</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>12.31</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>3604.25</v>
+        <v>3502.75</v>
       </c>
       <c r="I6" t="n">
         <v>3570.44160362327</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.01</v>
+        <v>-6.72</v>
       </c>
       <c r="L6" t="n">
-        <v>6.52</v>
+        <v>7.5</v>
       </c>
       <c r="M6" t="n">
         <v>1.9</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>8.42</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>3546.5</v>
+        <v>3634.5</v>
       </c>
       <c r="I7" t="n">
         <v>3613.633848594762</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.25</v>
+        <v>-3.76</v>
       </c>
       <c r="L7" t="n">
-        <v>1.55</v>
+        <v>4.49</v>
       </c>
       <c r="M7" t="n">
         <v>1.86</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>8.77</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44767.55208333334</v>
+        <v>44768.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>3765</v>
+        <v>3710.65</v>
       </c>
       <c r="I8" t="n">
         <v>3732.506915652746</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K8" t="n">
-        <v>3.59</v>
+        <v>2.1</v>
       </c>
       <c r="L8" t="n">
         <v>3.48</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.58</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44777.38541666666</v>
+        <v>44777.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>3821</v>
+        <v>3830</v>
       </c>
       <c r="I9" t="n">
         <v>3826.260276114191</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.97</v>
+        <v>-3.22</v>
       </c>
       <c r="L9" t="n">
         <v>4.21</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.68</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>4465</v>
+        <v>4369</v>
       </c>
       <c r="I10" t="n">
         <v>4369.93736300255</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K10" t="n">
-        <v>16.58</v>
+        <v>14.07</v>
       </c>
       <c r="L10" t="n">
         <v>3.08</v>
@@ -1011,7 +1130,7 @@
         <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
         <v>2</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.62</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44862.55208333334</v>
+        <v>44865.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>4384</v>
+        <v>4488.8</v>
       </c>
       <c r="I11" t="n">
         <v>4435.410374500898</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.34</v>
+        <v>-2.74</v>
       </c>
       <c r="L11" t="n">
         <v>3.25</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>5.46</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44881.55208333334</v>
+        <v>44882.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>4486.7</v>
+        <v>4401</v>
       </c>
       <c r="I12" t="n">
         <v>4425.221990861892</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.05</v>
+        <v>-1.96</v>
       </c>
       <c r="L12" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="M12" t="n">
         <v>1.3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="O12" t="n">
         <v>3.01</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.02</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44984.55208333334</v>
+        <v>44985.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>2785</v>
+        <v>2894</v>
       </c>
       <c r="I13" t="n">
         <v>2813.805162070275</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>102.1666666666667</v>
+        <v>103</v>
       </c>
       <c r="K13" t="n">
-        <v>36.72</v>
+        <v>34.24</v>
       </c>
       <c r="L13" t="n">
         <v>2.39</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.31</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44994.38541666666</v>
+        <v>44994.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>2837.8</v>
+        <v>2829</v>
       </c>
       <c r="I14" t="n">
         <v>2835.901203039506</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.94</v>
+        <v>-2.25</v>
       </c>
       <c r="L14" t="n">
         <v>4.62</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>5.92</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45026.38541666666</v>
+        <v>45026.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>2940</v>
+        <v>2980</v>
       </c>
       <c r="I15" t="n">
         <v>2949.71731641543</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>31.83333333333333</v>
+        <v>32</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.92</v>
+        <v>-5.34</v>
       </c>
       <c r="L15" t="n">
-        <v>4.55</v>
+        <v>5.55</v>
       </c>
       <c r="M15" t="n">
         <v>1.2</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>5.91</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45042.38541666666</v>
+        <v>45042.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>2849.95</v>
+        <v>2827.7</v>
       </c>
       <c r="I16" t="n">
         <v>2843.464583443989</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.36</v>
+        <v>-5.11</v>
       </c>
       <c r="L16" t="n">
-        <v>4.49</v>
+        <v>5.34</v>
       </c>
       <c r="M16" t="n">
         <v>0.76</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.83</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45064.38541666666</v>
+        <v>45064.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>2969</v>
+        <v>3000</v>
       </c>
       <c r="I17" t="n">
         <v>2987.221279206115</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>21.83333333333333</v>
+        <v>22</v>
       </c>
       <c r="K17" t="n">
-        <v>-5</v>
+        <v>-6.09</v>
       </c>
       <c r="L17" t="n">
         <v>7.51</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.27</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45100.38541666666</v>
+        <v>45100.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>4346.55</v>
+        <v>4330</v>
       </c>
       <c r="I18" t="n">
         <v>4343.402072153682</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>35.83333333333334</v>
+        <v>36</v>
       </c>
       <c r="K18" t="n">
-        <v>44.89</v>
+        <v>44.33</v>
       </c>
       <c r="L18" t="n">
         <v>1.03</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.01</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45140.55208333334</v>
+        <v>45141.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>4131</v>
+        <v>4344</v>
       </c>
       <c r="I19" t="n">
         <v>4247.973348718385</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>40</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K19" t="n">
-        <v>4.6</v>
+        <v>-0.32</v>
       </c>
       <c r="L19" t="n">
         <v>4.06</v>
@@ -1524,7 +1751,7 @@
         <v>0.76</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>7.84</v>
       </c>
       <c r="O19" t="n">
         <v>-2.59</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.32</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45187.38541666666</v>
+        <v>45187.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>4959.75</v>
+        <v>4925</v>
       </c>
       <c r="I20" t="n">
         <v>4934.313471157879</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K20" t="n">
-        <v>14.17</v>
+        <v>13.37</v>
       </c>
       <c r="L20" t="n">
         <v>5.82</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>5.31</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45194.55208333334</v>
+        <v>45195.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>4901.75</v>
+        <v>5066.85</v>
       </c>
       <c r="I21" t="n">
         <v>5049.489788649302</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>0.47</v>
+        <v>-2.88</v>
       </c>
       <c r="L21" t="n">
-        <v>0.88</v>
+        <v>3.96</v>
       </c>
       <c r="M21" t="n">
         <v>0.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.16</v>
+        <v>4.09</v>
       </c>
       <c r="O21" t="n">
         <v>-2.74</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.04</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45226.55208333334</v>
+        <v>45229.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>5360.05</v>
+        <v>5131.7</v>
       </c>
       <c r="I22" t="n">
         <v>5299.51899379758</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K22" t="n">
-        <v>5.79</v>
+        <v>1.28</v>
       </c>
       <c r="L22" t="n">
         <v>3.27</v>
@@ -1695,7 +1958,7 @@
         <v>2.06</v>
       </c>
       <c r="N22" t="n">
-        <v>1.7</v>
+        <v>4.76</v>
       </c>
       <c r="O22" t="n">
         <v>4.09</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>8.65</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45246.55208333334</v>
+        <v>45247.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>5429</v>
+        <v>5446.65</v>
       </c>
       <c r="I23" t="n">
         <v>5440.489193122723</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.79</v>
+        <v>-6.14</v>
       </c>
       <c r="L23" t="n">
-        <v>6.3</v>
+        <v>6.95</v>
       </c>
       <c r="M23" t="n">
         <v>1.12</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>4.9</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45309.55208333334</v>
+        <v>45310.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>6292.2</v>
+        <v>6149.9</v>
       </c>
       <c r="I24" t="n">
         <v>6287.423726827158</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>62.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K24" t="n">
-        <v>15.52</v>
+        <v>12.91</v>
       </c>
       <c r="L24" t="n">
         <v>3.34</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="N24" t="n">
         <v>3.38</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5.89</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45324.38541666666</v>
+        <v>45324.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>6197.05</v>
+        <v>6224</v>
       </c>
       <c r="I25" t="n">
         <v>6214.768490260509</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.77</v>
+        <v>-1.2</v>
       </c>
       <c r="L25" t="n">
         <v>3.22</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.65</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45350.38541666666</v>
+        <v>45350.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>6635</v>
+        <v>6538</v>
       </c>
       <c r="I26" t="n">
         <v>6569.117293701061</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K26" t="n">
-        <v>6.6</v>
+        <v>5.04</v>
       </c>
       <c r="L26" t="n">
         <v>1.58</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>7.87</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45352.38541666666</v>
+        <v>45355.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>6959.9</v>
+        <v>7122.1</v>
       </c>
       <c r="I27" t="n">
         <v>7052.407771102734</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.833333333333333</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.45</v>
+        <v>-8.93</v>
       </c>
       <c r="L27" t="n">
-        <v>6.68</v>
+        <v>9.26</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="N27" t="n">
         <v>4.31</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>7.78</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>6770.5</v>
+        <v>6598</v>
       </c>
       <c r="I28" t="n">
         <v>6717.366066509354</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.94</v>
+        <v>-7.36</v>
       </c>
       <c r="L28" t="n">
-        <v>5.87</v>
+        <v>7.91</v>
       </c>
       <c r="M28" t="n">
         <v>0.21</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>8.17</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45372.55208333334</v>
+        <v>45373.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>7065.2</v>
+        <v>7159.5</v>
       </c>
       <c r="I29" t="n">
         <v>7137.333324636891</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.08</v>
+        <v>-8.51</v>
       </c>
       <c r="L29" t="n">
-        <v>7.29</v>
+        <v>8.52</v>
       </c>
       <c r="M29" t="n">
         <v>1.26</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.27</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45397.55208333334</v>
+        <v>45398.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>7638.4</v>
+        <v>7496</v>
       </c>
       <c r="I30" t="n">
         <v>7498.000260300629</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K30" t="n">
-        <v>6.69</v>
+        <v>4.7</v>
       </c>
       <c r="L30" t="n">
         <v>1.85</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>6.52</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45404.55208333334</v>
+        <v>45405.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>7831.9</v>
+        <v>7872</v>
       </c>
       <c r="I31" t="n">
         <v>7837.113930394115</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.48</v>
+        <v>-5.02</v>
       </c>
       <c r="L31" t="n">
-        <v>4.72</v>
+        <v>5.3</v>
       </c>
       <c r="M31" t="n">
         <v>2.29</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.82</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>9885</v>
+        <v>8913.049999999999</v>
       </c>
       <c r="I32" t="n">
         <v>9349.36152372518</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K32" t="n">
-        <v>25.57</v>
+        <v>13.22</v>
       </c>
       <c r="L32" t="n">
         <v>1.91</v>
@@ -2265,7 +2648,7 @@
         <v>0.53</v>
       </c>
       <c r="N32" t="n">
-        <v>2.24</v>
+        <v>9.83</v>
       </c>
       <c r="O32" t="n">
         <v>-0.96</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>13.04</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>9820</v>
+        <v>10042.5</v>
       </c>
       <c r="I33" t="n">
         <v>9886.162915782606</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>-10.18</v>
+        <v>-12.67</v>
       </c>
       <c r="L33" t="n">
-        <v>10.6</v>
+        <v>13.18</v>
       </c>
       <c r="M33" t="n">
         <v>2.1</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>10.17</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45489.55208333334</v>
+        <v>45491.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>12550</v>
+        <v>12035.4</v>
       </c>
       <c r="I34" t="n">
         <v>12073.82448510157</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K34" t="n">
-        <v>24.97</v>
+        <v>19.84</v>
       </c>
       <c r="L34" t="n">
         <v>1.72</v>
       </c>
       <c r="M34" t="n">
-        <v>0.22</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>2.63</v>
+        <v>5.1</v>
       </c>
       <c r="O34" t="n">
         <v>1.83</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>6.64</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45503.38541666666</v>
+        <v>45503.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>11570</v>
+        <v>11964</v>
       </c>
       <c r="I35" t="n">
         <v>11812.16261529492</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>3.87</v>
+        <v>0.59</v>
       </c>
       <c r="L35" t="n">
         <v>3.69</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>9.06</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>11649.8</v>
+        <v>11084.95</v>
       </c>
       <c r="I36" t="n">
         <v>11343.70364328969</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.63</v>
+        <v>-7.35</v>
       </c>
       <c r="L36" t="n">
-        <v>4.59</v>
+        <v>8.48</v>
       </c>
       <c r="M36" t="n">
-        <v>1.28</v>
+        <v>6.01</v>
       </c>
       <c r="N36" t="n">
-        <v>3.31</v>
+        <v>4.58</v>
       </c>
       <c r="O36" t="n">
         <v>2.64</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>10.87</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45518.55208333334</v>
+        <v>45520.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>11890</v>
+        <v>12289.6</v>
       </c>
       <c r="I37" t="n">
         <v>12151.35072238834</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.26</v>
+        <v>-10.87</v>
       </c>
       <c r="L37" t="n">
-        <v>9.6</v>
+        <v>11.41</v>
       </c>
       <c r="M37" t="n">
         <v>2.55</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.58</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45534.55208333334</v>
+        <v>45537.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>12934</v>
+        <v>12550</v>
       </c>
       <c r="I38" t="n">
         <v>12717.1875172828</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>5.24</v>
+        <v>2.12</v>
       </c>
       <c r="L38" t="n">
         <v>2.15</v>
@@ -2607,7 +3062,7 @@
         <v>0.03</v>
       </c>
       <c r="N38" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="O38" t="n">
         <v>3.96</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.56</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45548.38541666666</v>
+        <v>45548.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>12872</v>
+        <v>13027.85</v>
       </c>
       <c r="I39" t="n">
         <v>12910.12675849219</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.57</v>
+        <v>-3.81</v>
       </c>
       <c r="L39" t="n">
         <v>4.86</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>6.36</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45589.55208333334</v>
+        <v>45590.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>15044.95</v>
+        <v>13572</v>
       </c>
       <c r="I40" t="n">
         <v>14655.8817625151</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>41</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K40" t="n">
-        <v>15.48</v>
+        <v>4.18</v>
       </c>
       <c r="L40" t="n">
         <v>1.83</v>
@@ -2721,7 +3200,7 @@
         <v>2.1</v>
       </c>
       <c r="N40" t="n">
-        <v>4.17</v>
+        <v>7.35</v>
       </c>
       <c r="O40" t="n">
         <v>1.17</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>19.24</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45601.55208333334</v>
+        <v>45602.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>14414</v>
+        <v>15523.25</v>
       </c>
       <c r="I41" t="n">
         <v>15360.71598152002</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K41" t="n">
-        <v>-6.2</v>
+        <v>-14.38</v>
       </c>
       <c r="L41" t="n">
         <v>17.15</v>
@@ -2778,7 +3269,7 @@
         <v>5.68</v>
       </c>
       <c r="N41" t="n">
-        <v>5.23</v>
+        <v>8.44</v>
       </c>
       <c r="O41" t="n">
         <v>-7.35</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>12.73</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>18370</v>
+        <v>17994.85</v>
       </c>
       <c r="I42" t="n">
         <v>18060.40557821486</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K42" t="n">
-        <v>18.34</v>
+        <v>15.92</v>
       </c>
       <c r="L42" t="n">
         <v>6.59</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.54</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45674.55208333334</v>
+        <v>45677.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>17200</v>
+        <v>17471.35</v>
       </c>
       <c r="I43" t="n">
         <v>17224.42792885317</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K43" t="n">
-        <v>4.42</v>
+        <v>2.91</v>
       </c>
       <c r="L43" t="n">
         <v>3.92</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>7.9</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45677.55208333334</v>
+        <v>45678.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>17520.5</v>
+        <v>15248.95</v>
       </c>
       <c r="I44" t="n">
         <v>16319.88074775439</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0.28</v>
+        <v>-12.72</v>
       </c>
       <c r="L44" t="n">
-        <v>1.8</v>
+        <v>13.46</v>
       </c>
       <c r="M44" t="n">
-        <v>-0</v>
+        <v>1.55</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>13.67</v>
       </c>
       <c r="O44" t="n">
         <v>1.86</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>18.46</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45737.55208333334</v>
+        <v>45740.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>14050</v>
+        <v>14624.1</v>
       </c>
       <c r="I45" t="n">
         <v>14214.83527967675</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K45" t="n">
-        <v>7.86</v>
+        <v>4.1</v>
       </c>
       <c r="L45" t="n">
         <v>13.78</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45741.38541666666</v>
+        <v>45741.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>13799.9</v>
+        <v>13560.5</v>
       </c>
       <c r="I46" t="n">
         <v>13686.36981744762</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.64</v>
+        <v>-7.27</v>
       </c>
       <c r="L46" t="n">
-        <v>5.87</v>
+        <v>7.72</v>
       </c>
       <c r="M46" t="n">
         <v>-0</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>9.41</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>13265</v>
+        <v>14263.35</v>
       </c>
       <c r="I47" t="n">
         <v>13733.1315749274</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>15</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>2.18</v>
+        <v>-5.18</v>
       </c>
       <c r="L47" t="n">
-        <v>2.27</v>
+        <v>5.45</v>
       </c>
       <c r="M47" t="n">
-        <v>2.93</v>
+        <v>5.14</v>
       </c>
       <c r="N47" t="n">
-        <v>4.22</v>
+        <v>7.5</v>
       </c>
       <c r="O47" t="n">
         <v>-7.12</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>11.64</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>16040</v>
+        <v>15550</v>
       </c>
       <c r="I48" t="n">
         <v>15627.58207443855</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>12.46</v>
+        <v>9.02</v>
       </c>
       <c r="L48" t="n">
         <v>4.93</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45792.38541666666</v>
+        <v>45792.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>16075</v>
+        <v>16350</v>
       </c>
       <c r="I49" t="n">
         <v>16239.36892287042</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.38</v>
+        <v>-5.14</v>
       </c>
       <c r="L49" t="n">
-        <v>6.17</v>
+        <v>6.3</v>
       </c>
       <c r="M49" t="n">
         <v>4.86</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>7.28</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45797.55208333334</v>
+        <v>45798.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>16630</v>
+        <v>15610</v>
       </c>
       <c r="I50" t="n">
         <v>15791.53930804051</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>1.71</v>
+        <v>-4.53</v>
       </c>
       <c r="L50" t="n">
-        <v>1.93</v>
+        <v>6.61</v>
       </c>
       <c r="M50" t="n">
-        <v>0.04</v>
+        <v>0.38</v>
       </c>
       <c r="N50" t="n">
-        <v>0.24</v>
+        <v>6.25</v>
       </c>
       <c r="O50" t="n">
         <v>1.27</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,25 +3938,25 @@
         <v>10.87</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>14540</v>
+        <v>14708</v>
       </c>
       <c r="I51" t="n">
         <v>14707.70704218393</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K51" t="n">
-        <v>6.85</v>
+        <v>5.78</v>
       </c>
       <c r="L51" t="n">
         <v>6.61</v>
       </c>
       <c r="M51" t="n">
-        <v>0.73</v>
+        <v>1.11</v>
       </c>
       <c r="N51" t="n">
         <v>3.56</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.51</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45876.55208333334</v>
+        <v>45877.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>16675</v>
+        <v>16184</v>
       </c>
       <c r="I52" t="n">
         <v>16322.42800012242</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K52" t="n">
-        <v>13.37</v>
+        <v>10.04</v>
       </c>
       <c r="L52" t="n">
         <v>4.59</v>
@@ -3405,7 +4028,7 @@
         <v>2.6</v>
       </c>
       <c r="N52" t="n">
-        <v>2.59</v>
+        <v>5.19</v>
       </c>
       <c r="O52" t="n">
         <v>-0.28</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>7.08</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>16190</v>
+        <v>16811</v>
       </c>
       <c r="I53" t="n">
         <v>16744.04427060235</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.04</v>
+        <v>-3.87</v>
       </c>
       <c r="L53" t="n">
-        <v>3.19</v>
+        <v>4.5</v>
       </c>
       <c r="M53" t="n">
-        <v>0.49</v>
+        <v>1.91</v>
       </c>
       <c r="N53" t="n">
-        <v>1.61</v>
+        <v>3.62</v>
       </c>
       <c r="O53" t="n">
         <v>-5.19</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.29</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>18187</v>
+        <v>17650</v>
       </c>
       <c r="I54" t="n">
         <v>17875.34601325449</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K54" t="n">
-        <v>8.19</v>
+        <v>4.99</v>
       </c>
       <c r="L54" t="n">
         <v>2.35</v>
@@ -3519,7 +4166,7 @@
         <v>0.84</v>
       </c>
       <c r="N54" t="n">
-        <v>2.21</v>
+        <v>3.66</v>
       </c>
       <c r="O54" t="n">
         <v>3.62</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>5.14</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45939.55208333334</v>
+        <v>45940.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>17083</v>
+        <v>17358</v>
       </c>
       <c r="I55" t="n">
         <v>17277.86265298302</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K55" t="n">
-        <v>3.21</v>
+        <v>1.65</v>
       </c>
       <c r="L55" t="n">
         <v>3.28</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>5.27</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45943.55208333334</v>
+        <v>45944.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>17232</v>
+        <v>16486</v>
       </c>
       <c r="I56" t="n">
         <v>16577.74292460842</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.73</v>
+        <v>-5.02</v>
       </c>
       <c r="L56" t="n">
-        <v>3.04</v>
+        <v>5.23</v>
       </c>
       <c r="M56" t="n">
         <v>0.09</v>
       </c>
       <c r="N56" t="n">
-        <v>1.28</v>
+        <v>3.61</v>
       </c>
       <c r="O56" t="n">
         <v>2.18</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.52</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45973.55208333334</v>
+        <v>45974.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>15300</v>
+        <v>15529</v>
       </c>
       <c r="I57" t="n">
         <v>15486.82876461541</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K57" t="n">
-        <v>7.19</v>
+        <v>5.8</v>
       </c>
       <c r="L57" t="n">
         <v>4.93</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>5.11</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45981.55208333334</v>
+        <v>45982.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>15300</v>
+        <v>15020</v>
       </c>
       <c r="I58" t="n">
         <v>15084.43202884393</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.47</v>
+        <v>-3.28</v>
       </c>
       <c r="L58" t="n">
-        <v>1.94</v>
+        <v>3.66</v>
       </c>
       <c r="M58" t="n">
         <v>0.2</v>
       </c>
       <c r="N58" t="n">
-        <v>1.76</v>
+        <v>2.29</v>
       </c>
       <c r="O58" t="n">
         <v>0.2</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>5.49</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46003.55208333334</v>
+        <v>46006.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>13365</v>
+        <v>13732</v>
       </c>
       <c r="I59" t="n">
         <v>13682.75243187827</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K59" t="n">
-        <v>11.02</v>
+        <v>8.58</v>
       </c>
       <c r="L59" t="n">
         <v>1.93</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>9.93</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46015.38541666666</v>
+        <v>46015.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>13000</v>
+        <v>12649</v>
       </c>
       <c r="I60" t="n">
         <v>12686.8705865002</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K60" t="n">
-        <v>-5.33</v>
+        <v>-7.89</v>
       </c>
       <c r="L60" t="n">
         <v>8.83</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>8.75</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>10354</v>
+        <v>11050</v>
       </c>
       <c r="I61" t="n">
         <v>10931.72016615008</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>40</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K61" t="n">
-        <v>18.14</v>
+        <v>12.64</v>
       </c>
       <c r="L61" t="n">
         <v>2.77</v>
       </c>
       <c r="M61" t="n">
-        <v>1.49</v>
+        <v>7.2</v>
       </c>
       <c r="N61" t="n">
-        <v>2.63</v>
+        <v>6.56</v>
       </c>
       <c r="O61" t="n">
         <v>-1.6</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>11.9</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46073.55208333334</v>
+        <v>46076.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>11020</v>
+        <v>10709</v>
       </c>
       <c r="I62" t="n">
         <v>10959.93916546816</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.27</v>
+        <v>-3.09</v>
       </c>
       <c r="L62" t="n">
-        <v>1.79</v>
+        <v>3.67</v>
       </c>
       <c r="M62" t="n">
         <v>0.86</v>
       </c>
       <c r="N62" t="n">
-        <v>2.79</v>
+        <v>3.72</v>
       </c>
       <c r="O62" t="n">
         <v>6.56</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>9.1</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46091.38541666666</v>
+        <v>46091.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>10384</v>
+        <v>11035</v>
       </c>
       <c r="I63" t="n">
         <v>10551.69646024897</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K63" t="n">
-        <v>3.03</v>
+        <v>-3.04</v>
       </c>
       <c r="L63" t="n">
         <v>3.93</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>12.38</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46111.38541666666</v>
+        <v>46111.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>9900</v>
+        <v>9638</v>
       </c>
       <c r="I64" t="n">
         <v>9806.227782042986</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K64" t="n">
-        <v>-10.29</v>
+        <v>-12.66</v>
       </c>
       <c r="L64" t="n">
-        <v>11.3</v>
+        <v>13</v>
       </c>
       <c r="M64" t="n">
         <v>2.01</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>9.65</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46120.38541666666</v>
+        <v>46120.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>10516</v>
+        <v>10699</v>
       </c>
       <c r="I65" t="n">
         <v>10567.83934977648</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K65" t="n">
-        <v>-9.109999999999999</v>
+        <v>-11.01</v>
       </c>
       <c r="L65" t="n">
-        <v>10.86</v>
+        <v>11.12</v>
       </c>
       <c r="M65" t="n">
         <v>4.79</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>10781</v>
+        <v>10359</v>
       </c>
       <c r="I66" t="n">
         <v>10767.67496046632</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K66" t="n">
-        <v>0.77</v>
+        <v>-3.18</v>
       </c>
       <c r="L66" t="n">
         <v>3.84</v>
@@ -4203,7 +4994,7 @@
         <v>2.39</v>
       </c>
       <c r="N66" t="n">
-        <v>3.86</v>
+        <v>6.13</v>
       </c>
       <c r="O66" t="n">
         <v>5.72</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>10</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46155.38541666666</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>10911</v>
+        <v>11129</v>
       </c>
       <c r="I67" t="n">
         <v>11089.32069176323</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>-5.33</v>
+        <v>-7.43</v>
       </c>
       <c r="L67" t="n">
-        <v>6.48</v>
+        <v>8.43</v>
       </c>
       <c r="M67" t="n">
         <v>1.33</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>9.93</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46196.38541666666</v>
+        <v>46196.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>11962</v>
+        <v>11906</v>
       </c>
       <c r="I68" t="n">
         <v>11951.19184421247</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>40.83333333333334</v>
+        <v>41</v>
       </c>
       <c r="K68" t="n">
-        <v>7.48</v>
+        <v>6.98</v>
       </c>
       <c r="L68" t="n">
         <v>5.02</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>6.85</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46206.55208333334</v>
+        <v>46209.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>12440</v>
+        <v>13085</v>
       </c>
       <c r="I69" t="n">
         <v>12538.86003332393</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K69" t="n">
-        <v>-4.49</v>
+        <v>-9.9</v>
       </c>
       <c r="L69" t="n">
-        <v>5.62</v>
+        <v>10.54</v>
       </c>
       <c r="M69" t="n">
         <v>0.67</v>
       </c>
       <c r="N69" t="n">
-        <v>3.73</v>
+        <v>7.07</v>
       </c>
       <c r="O69" t="n">
         <v>-3.39</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46269.38541666666</v>
+        <v>46269.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>14265</v>
+        <v>14160</v>
       </c>
       <c r="I70" t="n">
         <v>14184.21276011433</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>60</v>
+        <v>60.16666666666666</v>
       </c>
       <c r="K70" t="n">
-        <v>9.02</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L70" t="n">
         <v>5.58</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>69</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7452,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.6</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7462,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7472,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>102.2</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7482,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7492,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7502,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44.5</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="11">
@@ -6653,7 +7512,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -6663,7 +7522,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -6673,7 +7532,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>65.2</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="14">
@@ -6683,7 +7542,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.91</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.07</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7562,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7572,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>44.89</v>
+        <v>44.33</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7582,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7592,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.7</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7602,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.93</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="21">
@@ -6763,7 +7622,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7632,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7642,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="25">
@@ -6793,7 +7652,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="26">
@@ -6803,7 +7662,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.68</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7672,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.49</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7682,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
